--- a/laporan_padel_dki_jakarta_2026-09-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-20.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.188.500</t>
+          <t>Rp16.463.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.854.000</t>
+          <t>Rp3.618.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.065.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp12.305.000</t>
+          <t>Rp12.695.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>85</v>
       </c>
       <c r="D78" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.097.000</t>
+          <t>Rp2.694.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>48</v>
       </c>
       <c r="D40" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp8.557.000</t>
+          <t>Rp8.756.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp1.392.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.425.000</t>
+          <t>Rp9.700.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.066.000</t>
+          <t>Rp3.566.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.533.000</t>
+          <t>Rp7.695.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.160.000</t>
+          <t>Rp12.320.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.260.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.745.000</t>
+          <t>Rp4.895.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.625.000</t>
+          <t>Rp4.220.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-20.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.820.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.990.000</t>
+          <t>Rp7.520.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp585.000</t>
+          <t>Rp390.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>34</v>
       </c>
       <c r="D92" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.895.000</t>
+          <t>Rp3.015.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp7.920.000</t>
+          <t>Rp8.580.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.656.000</t>
+          <t>Rp1.729.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.630.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp188.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp297.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp1.570.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.130.000</t>
+          <t>Rp3.430.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp4.590.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-20.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.240.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.653.000</t>
+          <t>Rp4.851.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.520.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.505.000</t>
+          <t>Rp4.674.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.463.500</t>
+          <t>Rp16.541.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.241.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp15.390.000</t>
+          <t>Rp15.640.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp390.000</t>
+          <t>Rp195.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.096.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.680.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.540.000</t>
+          <t>Rp5.110.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>45</v>
       </c>
       <c r="D44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>96</v>
       </c>
       <c r="D46" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.578.000</t>
+          <t>Rp7.828.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.555.554</t>
+          <t>Rp1.111.110</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp605.000</t>
+          <t>Rp765.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.788.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp2.065.000</t>
+          <t>Rp2.385.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp335.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>153</v>
       </c>
       <c r="D59" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.492.000</t>
+          <t>Rp1.790.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.431.000</t>
+          <t>Rp1.749.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>34</v>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.730.000</t>
+          <t>Rp1.540.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>96</v>
       </c>
       <c r="D73" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.510.000</t>
+          <t>Rp4.610.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp12.695.000</t>
+          <t>Rp11.525.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>85</v>
       </c>
       <c r="D78" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>96</v>
       </c>
       <c r="D83" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp7.110.000</t>
+          <t>Rp7.860.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.780.000</t>
+          <t>Rp10.114.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp9.040.000</t>
+          <t>Rp9.830.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.695.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.560.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp17.650.000</t>
+          <t>Rp18.350.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp21.505.000</t>
+          <t>Rp23.155.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.296.000</t>
+          <t>Rp2.795.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp8.475.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp8.580.000</t>
+          <t>Rp9.460.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>144</v>
       </c>
       <c r="D58" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.729.000</t>
+          <t>Rp1.818.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>92</v>
       </c>
       <c r="D68" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp5.765.000</t>
+          <t>Rp6.340.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.090.000</t>
+          <t>Rp17.710.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp13.900.000</t>
+          <t>Rp14.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.392.000</t>
+          <t>Rp1.591.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.630.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp8.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.285.000</t>
+          <t>Rp15.835.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp10.500.000</t>
+          <t>Rp9.100.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.560.000</t>
+          <t>Rp17.005.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp3.760.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.566.000</t>
+          <t>Rp4.066.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.695.000</t>
+          <t>Rp7.209.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.587.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp5.920.000</t>
+          <t>Rp6.620.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp3.760.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D46" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp3.160.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.320.000</t>
+          <t>Rp12.510.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.186.000</t>
+          <t>Rp4.784.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.945.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.430.000</t>
+          <t>Rp3.880.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp4.280.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.230.000</t>
+          <t>Rp3.610.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp11.130.000</t>
+          <t>Rp12.810.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.175.000</t>
+          <t>Rp3.795.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.520.000</t>
+          <t>Rp5.360.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp2.590.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp4.995.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp676.000</t>
+          <t>Rp845.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp4.179.000</t>
+          <t>Rp3.781.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-20.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>184</v>
       </c>
       <c r="D4" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.600.000</t>
+          <t>Rp13.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.851.000</t>
+          <t>Rp5.049.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.408.000</t>
+          <t>Rp1.496.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp13.830.000</t>
+          <t>Rp14.430.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.541.500</t>
+          <t>Rp16.954.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.870.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.660.000</t>
+          <t>Rp1.870.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.237.000</t>
+          <t>Rp4.233.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp15.640.000</t>
+          <t>Rp15.765.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp32.041.000</t>
+          <t>Rp33.535.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.126.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp3.230.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.354.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.680.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.654.000</t>
+          <t>Rp4.833.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.788.000</t>
+          <t>Rp3.958.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp630.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>96</v>
       </c>
       <c r="D46" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.828.000</t>
+          <t>Rp8.136.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.111.110</t>
+          <t>Rp1.666.665</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>36</v>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp2.385.000</t>
+          <t>Rp2.505.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp335.000</t>
+          <t>Rp510.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp347.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>153</v>
       </c>
       <c r="D59" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp2.139.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.749.000</t>
+          <t>Rp2.167.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.478.000</t>
+          <t>Rp3.498.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp2.546.000</t>
+          <t>Rp3.243.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp200.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2528,16 +2528,16 @@
         <v>128</v>
       </c>
       <c r="D68" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp199.000</t>
+          <t>Rp1.393.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>96</v>
       </c>
       <c r="D69" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.630.000</t>
+          <t>Rp6.230.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>96</v>
       </c>
       <c r="D77" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,21 +2838,21 @@
         <v>85</v>
       </c>
       <c r="D78" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2900,16 +2900,16 @@
         <v>36</v>
       </c>
       <c r="D80" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>36</v>
       </c>
       <c r="D89" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp7.860.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>32</v>
       </c>
       <c r="D96" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.349.000</t>
+          <t>Rp2.511.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.249.011</t>
+          <t>Rp18.425.011</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.114.000</t>
+          <t>Rp12.448.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp13.250.000</t>
+          <t>Rp13.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.015.000</t>
+          <t>Rp3.255.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.694.000</t>
+          <t>Rp2.869.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.385.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>69</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.610.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp120.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.093.000</t>
+          <t>Rp3.289.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.770.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp11.800.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.795.000</t>
+          <t>Rp3.395.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>32</v>
       </c>
       <c r="D50" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp1.664.000</t>
+          <t>Rp3.324.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.475.000</t>
+          <t>Rp8.725.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp8.756.000</t>
+          <t>Rp9.154.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp9.460.000</t>
+          <t>Rp10.285.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp10.200.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>92</v>
       </c>
       <c r="D68" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp6.340.000</t>
+          <t>Rp5.990.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.925.000</t>
+          <t>Rp5.325.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>28</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.710.000</t>
+          <t>Rp16.170.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp7.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp14.800.000</t>
+          <t>Rp19.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.005.000</t>
+          <t>Rp1.675.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.670.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp188.000</t>
+          <t>Rp752.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>68</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp2.145.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp16.150.000</t>
+          <t>Rp16.530.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.515.000</t>
+          <t>Rp14.765.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp564.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.835.000</t>
+          <t>Rp16.860.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp9.650.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.005.000</t>
+          <t>Rp17.345.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp4.136.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.700.000</t>
+          <t>Rp10.300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.066.000</t>
+          <t>Rp4.154.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.489.000</t>
+          <t>Rp1.638.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.850.000</t>
+          <t>Rp22.550.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.800.000</t>
+          <t>Rp8.200.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.209.000</t>
+          <t>Rp7.290.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.570.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp18.475.000</t>
+          <t>Rp19.475.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp4.136.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp18.369.000</t>
+          <t>Rp22.409.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>128</v>
       </c>
       <c r="D40" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.691.000</t>
+          <t>Rp3.887.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.775.000</t>
+          <t>Rp9.250.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp8.070.000</t>
+          <t>Rp8.320.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp4.440.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>48</v>
       </c>
       <c r="D49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.510.000</t>
+          <t>Rp13.160.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.945.000</t>
+          <t>Rp5.690.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.880.000</t>
+          <t>Rp4.215.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.280.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp580.000</t>
+          <t>Rp870.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp12.810.000</t>
+          <t>Rp12.600.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.838.000</t>
+          <t>Rp4.276.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.220.000</t>
+          <t>Rp4.880.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.795.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.590.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.995.000</t>
+          <t>Rp5.130.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.781.000</t>
+          <t>Rp4.179.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-20.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp8.225.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.954.000</t>
+          <t>Rp17.229.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.870.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.618.000</t>
+          <t>Rp3.914.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp630.000</t>
+          <t>Rp765.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp425.000</t>
+          <t>Rp575.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>36</v>
       </c>
       <c r="D53" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.788.000</t>
+          <t>Rp1.937.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp2.505.000</t>
+          <t>Rp2.705.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.498.000</t>
+          <t>Rp3.698.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>96</v>
       </c>
       <c r="D69" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp6.230.000</t>
+          <t>Rp6.380.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>32</v>
       </c>
       <c r="D96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.448.000</t>
+          <t>Rp14.004.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp13.800.000</t>
+          <t>Rp14.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp297.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>144</v>
       </c>
       <c r="D58" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.770.000</t>
+          <t>Rp5.310.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.170.000</t>
+          <t>Rp19.635.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp16.530.000</t>
+          <t>Rp16.830.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.550.000</t>
+          <t>Rp22.950.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.290.000</t>
+          <t>Rp7.371.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.620.000</t>
+          <t>Rp8.540.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.440.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.319.500</t>
+          <t>Rp12.634.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.895.000</t>
+          <t>Rp5.045.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-20.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-20.xlsx
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.290.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp15.765.000</t>
+          <t>Rp16.070.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp745.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.425.011</t>
+          <t>Rp18.600.011</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.395.000</t>
+          <t>Rp3.695.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.250.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.591.000</t>
+          <t>Rp1.690.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.860.000</t>
+          <t>Rp17.055.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.950.000</t>
+          <t>Rp23.350.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.371.000</t>
+          <t>Rp7.452.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.725.000</t>
+          <t>Rp4.023.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7878,16 +7878,16 @@
         <v>80</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp3.549.000</t>
+          <t>Rp3.718.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.160.000</t>
+          <t>Rp13.660.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp12.600.000</t>
+          <t>Rp12.810.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp3.515.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
